--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T03:04:10+00:00</t>
+    <t>2026-07-21T03:24:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T03:24:49+00:00</t>
+    <t>2026-07-21T03:34:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T03:34:20+00:00</t>
+    <t>2026-07-21T12:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:10:06+00:00</t>
+    <t>2026-07-21T12:21:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:21:04+00:00</t>
+    <t>2026-07-21T12:31:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:31:15+00:00</t>
+    <t>2026-07-21T13:03:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:03:45+00:00</t>
+    <t>2026-07-21T13:39:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:39:22+00:00</t>
+    <t>2026-07-21T13:58:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:58:44+00:00</t>
+    <t>2026-07-21T14:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T14:24:33+00:00</t>
+    <t>2026-07-21T14:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T14:33:42+00:00</t>
+    <t>2026-07-21T14:46:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T14:46:27+00:00</t>
+    <t>2026-07-21T15:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:31:26+00:00</t>
+    <t>2026-07-21T16:19:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:19:05+00:00</t>
+    <t>2026-07-21T16:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:38:11+00:00</t>
+    <t>2026-07-21T16:50:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-agrosus-dias-aplicacao-mes.xlsx
+++ b/ValueSet-agrosus-dias-aplicacao-mes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:50:13+00:00</t>
+    <t>2026-07-21T18:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
